--- a/dell/dist/20261025_戴爾模型_v0.1.xlsx
+++ b/dell/dist/20261025_戴爾模型_v0.1.xlsx
@@ -5133,7 +5133,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6300,7 +6300,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6480,7 +6480,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6601,7 +6601,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6722,7 +6722,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6843,7 +6843,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6964,7 +6964,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -17693,7 +17693,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -17845,7 +17845,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -33702,7 +33702,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -33778,7 +33778,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -33816,7 +33816,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.1.xlsx</t>
     </r>
   </si>
   <si>

--- a/dell/dist/20261025_戴爾模型_v0.1.xlsx
+++ b/dell/dist/20261025_戴爾模型_v0.1.xlsx
@@ -7068,7 +7068,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -7087,7 +7087,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -33721,7 +33721,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -33740,7 +33740,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -35066,7 +35066,7 @@
         <v>73</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>108.333333</v>
+        <v>104.166667</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>116.666667</v>
@@ -37512,7 +37512,7 @@
         <v>106</v>
       </c>
       <c r="C12" s="23" t="n">
-        <v>634.616531285011</v>
+        <v>634.61653128501</v>
       </c>
       <c r="D12" s="23" t="n">
         <v>1139.08069210867</v>
@@ -44081,35 +44081,35 @@
       </c>
       <c r="C9" s="21" t="n">
         <f aca="false">E207</f>
-        <v>240.708069669222</v>
+        <v>238.655629792039</v>
       </c>
       <c r="D9" s="22" t="n">
         <f aca="false">E217</f>
-        <v>0.105107974623159</v>
+        <v>0.105145796389273</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">E221</f>
-        <v>30.1884517926477</v>
+        <v>29.9418149308747</v>
       </c>
       <c r="F9" s="17" t="n">
         <f aca="false">E9/E$4-1</f>
-        <v>-0.000373022188972616</v>
+        <v>-0.00853988223348112</v>
       </c>
       <c r="G9" s="21" t="n">
         <f aca="false">F207</f>
-        <v>251.393018177524</v>
+        <v>248.712118891814</v>
       </c>
       <c r="H9" s="22" t="n">
         <f aca="false">F217</f>
-        <v>0.105023086338796</v>
+        <v>0.105069576584148</v>
       </c>
       <c r="I9" s="18" t="n">
         <f aca="false">F221</f>
-        <v>32.4773643795399</v>
+        <v>32.1452434028259</v>
       </c>
       <c r="J9" s="17" t="n">
         <f aca="false">I9/I$4-1</f>
-        <v>-0.000466866032101443</v>
+        <v>-0.0106883210994507</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48687,19 +48687,19 @@
       </c>
       <c r="D195" s="21" t="n">
         <f aca="false">D193*v_gb_lo+D194*v_vr_lo</f>
-        <v>593.19444625</v>
+        <v>582.98611455</v>
       </c>
       <c r="E195" s="21" t="n">
         <f aca="false">E193*v_gb_lo+E194*v_vr_lo</f>
-        <v>1086.6666648</v>
+        <v>1050.000004</v>
       </c>
       <c r="F195" s="21" t="n">
         <f aca="false">F193*v_gb_lo+F194*v_vr_lo</f>
-        <v>1219.444441</v>
+        <v>1173.611115</v>
       </c>
       <c r="G195" s="21" t="n">
         <f aca="false">G193*v_gb_lo+G194*v_vr_lo</f>
-        <v>1384.30555145</v>
+        <v>1331.59722655</v>
       </c>
       <c r="J195" s="5" t="s">
         <v>395</v>
@@ -48714,7 +48714,7 @@
       </c>
       <c r="D196" s="22" t="n">
         <f aca="false">a27_ai/D195</f>
-        <v>0.124748302125561</v>
+        <v>0.1269326972858</v>
       </c>
       <c r="J196" s="8" t="s">
         <v>397</v>
@@ -48777,19 +48777,19 @@
       </c>
       <c r="D199" s="22" t="n">
         <f aca="false">$D$196*D197*D198</f>
-        <v>0.124748302125561</v>
+        <v>0.1269326972858</v>
       </c>
       <c r="E199" s="22" t="n">
         <f aca="false">$D$196*E197*E198</f>
-        <v>0.112273471913005</v>
+        <v>0.11423942755722</v>
       </c>
       <c r="F199" s="22" t="n">
         <f aca="false">$D$196*F197*F198</f>
-        <v>0.106036056806727</v>
+        <v>0.10789279269293</v>
       </c>
       <c r="G199" s="22" t="n">
         <f aca="false">$D$196*G197*G198</f>
-        <v>0.099798641700449</v>
+        <v>0.10154615782864</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48809,15 +48809,15 @@
       </c>
       <c r="E200" s="21" t="n">
         <f aca="false">E195*E199</f>
-        <v>122.003839269222</v>
+        <v>119.951399392039</v>
       </c>
       <c r="F200" s="21" t="n">
         <f aca="false">F195*F199</f>
-        <v>129.305080018524</v>
+        <v>126.624180732814</v>
       </c>
       <c r="G200" s="21" t="n">
         <f aca="false">G195*G199</f>
-        <v>138.151813733101</v>
+        <v>135.218582131426</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48898,15 +48898,15 @@
       </c>
       <c r="E204" s="21" t="n">
         <f aca="false">E200+E202+E203</f>
-        <v>177.969520969222</v>
+        <v>175.917081092039</v>
       </c>
       <c r="F204" s="21" t="n">
         <f aca="false">F200+F202+F203</f>
-        <v>186.795053016524</v>
+        <v>184.114153730814</v>
       </c>
       <c r="G204" s="21" t="n">
         <f aca="false">G200+G202+G203</f>
-        <v>197.577074306321</v>
+        <v>194.643842704646</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48985,23 +48985,23 @@
       </c>
       <c r="E207" s="21" t="n">
         <f aca="false">E204+E205+E206</f>
-        <v>240.708069669222</v>
+        <v>238.655629792039</v>
       </c>
       <c r="F207" s="21" t="n">
         <f aca="false">F204+F205+F206</f>
-        <v>251.393018177524</v>
+        <v>248.712118891814</v>
       </c>
       <c r="G207" s="21" t="n">
         <f aca="false">G204+G205+G206</f>
-        <v>264.090238422151</v>
+        <v>261.157006820476</v>
       </c>
       <c r="H207" s="25" t="n">
         <f aca="false">G207*(1+H208)</f>
-        <v>278.682207804156</v>
+        <v>275.525515410442</v>
       </c>
       <c r="I207" s="25" t="n">
         <f aca="false">H207*(1+I208)</f>
-        <v>295.403140272405</v>
+        <v>292.057046335069</v>
       </c>
       <c r="J207" s="8" t="s">
         <v>405</v>
@@ -49020,19 +49020,19 @@
       </c>
       <c r="E208" s="17" t="n">
         <f aca="false">E207/D207-1</f>
-        <v>0.25368786286053</v>
+        <v>0.242998071833536</v>
       </c>
       <c r="F208" s="17" t="n">
         <f aca="false">F207/E207-1</f>
-        <v>0.0443896564123709</v>
+        <v>0.0421380761415007</v>
       </c>
       <c r="G208" s="17" t="n">
         <f aca="false">G207/F207-1</f>
-        <v>0.0505074497958462</v>
+        <v>0.050037320192168</v>
       </c>
       <c r="H208" s="26" t="n">
         <f aca="false">$G208+(fade_gA-$G208)*1/2</f>
-        <v>0.0552537248979231</v>
+        <v>0.055018660096084</v>
       </c>
       <c r="I208" s="26" t="n">
         <f aca="false">$G208+(fade_gA-$G208)*2/2</f>
@@ -49056,15 +49056,15 @@
       </c>
       <c r="E209" s="17" t="n">
         <f aca="false">E200/E207</f>
-        <v>0.506853963960901</v>
+        <v>0.502612905032087</v>
       </c>
       <c r="F209" s="17" t="n">
         <f aca="false">F200/F207</f>
-        <v>0.514354300512887</v>
+        <v>0.509119464290735</v>
       </c>
       <c r="G209" s="17" t="n">
         <f aca="false">G200/G207</f>
-        <v>0.523123514744471</v>
+        <v>0.517767391262749</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49148,15 +49148,15 @@
       </c>
       <c r="E213" s="27" t="n">
         <f aca="false">E200*E211+(E202+E203)*E212</f>
-        <v>20.9616992693822</v>
+        <v>20.7549978482674</v>
       </c>
       <c r="F213" s="27" t="n">
         <f aca="false">F200*F211+(F202+F203)*F212</f>
-        <v>21.9332730917586</v>
+        <v>21.6632794620391</v>
       </c>
       <c r="G213" s="27" t="n">
         <f aca="false">G200*G211+(G202+G203)*G212</f>
-        <v>23.1241980850536</v>
+        <v>22.8287920430715</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49232,15 +49232,15 @@
       </c>
       <c r="E216" s="27" t="n">
         <f aca="false">E213+E215</f>
-        <v>25.3003376783822</v>
+        <v>25.0936362572675</v>
       </c>
       <c r="F216" s="27" t="n">
         <f aca="false">F213+F215</f>
-        <v>26.4020706530286</v>
+        <v>26.1320770233091</v>
       </c>
       <c r="G216" s="27" t="n">
         <f aca="false">G213+G215</f>
-        <v>27.7270595731617</v>
+        <v>27.4316535311796</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49260,15 +49260,15 @@
       </c>
       <c r="E217" s="22" t="n">
         <f aca="false">E216/E207</f>
-        <v>0.105107974623159</v>
+        <v>0.105145796389273</v>
       </c>
       <c r="F217" s="22" t="n">
         <f aca="false">F216/F207</f>
-        <v>0.105023086338796</v>
+        <v>0.105069576584148</v>
       </c>
       <c r="G217" s="22" t="n">
         <f aca="false">G216/G207</f>
-        <v>0.104990853652227</v>
+        <v>0.105038933724787</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49316,23 +49316,23 @@
       </c>
       <c r="E219" s="27" t="n">
         <f aca="false">E216*E218</f>
-        <v>18.9752532587866</v>
+        <v>18.8202271929506</v>
       </c>
       <c r="F219" s="27" t="n">
         <f aca="false">F216*F218</f>
-        <v>19.8015529897715</v>
+        <v>19.5990577674818</v>
       </c>
       <c r="G219" s="27" t="n">
         <f aca="false">G216*G218</f>
-        <v>20.7952946798713</v>
+        <v>20.5737401483847</v>
       </c>
       <c r="H219" s="28" t="n">
         <f aca="false">H207*H223</f>
-        <v>21.9440853341011</v>
+        <v>21.7004877642237</v>
       </c>
       <c r="I219" s="28" t="n">
         <f aca="false">I207*I223</f>
-        <v>23.2604900067332</v>
+        <v>22.9970135097696</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49388,23 +49388,23 @@
       </c>
       <c r="E221" s="27" t="n">
         <f aca="false">E219/E220</f>
-        <v>30.1884517926477</v>
+        <v>29.9418149308747</v>
       </c>
       <c r="F221" s="27" t="n">
         <f aca="false">F219/F220</f>
-        <v>32.4773643795399</v>
+        <v>32.1452434028259</v>
       </c>
       <c r="G221" s="27" t="n">
         <f aca="false">G219/G220</f>
-        <v>35.1621053056285</v>
+        <v>34.7874857637082</v>
       </c>
       <c r="H221" s="30" t="n">
         <f aca="false">H219/H220</f>
-        <v>38.2521227290797</v>
+        <v>37.8274924017006</v>
       </c>
       <c r="I221" s="30" t="n">
         <f aca="false">I219/I220</f>
-        <v>41.800856653333</v>
+        <v>41.3273694964456</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49420,23 +49420,23 @@
       </c>
       <c r="E222" s="17" t="n">
         <f aca="false">E221/D221-1</f>
-        <v>0.183860854613634</v>
+        <v>0.174188820818615</v>
       </c>
       <c r="F222" s="17" t="n">
         <f aca="false">F221/E221-1</f>
-        <v>0.0758208007026591</v>
+        <v>0.0735903443741857</v>
       </c>
       <c r="G222" s="17" t="n">
         <f aca="false">G221/F221-1</f>
-        <v>0.0826649876730745</v>
+        <v>0.0821969934329385</v>
       </c>
       <c r="H222" s="26" t="n">
         <f aca="false">H221/G221-1</f>
-        <v>0.0878791925737339</v>
+        <v>0.0873879376808502</v>
       </c>
       <c r="I222" s="26" t="n">
         <f aca="false">I221/H221-1</f>
-        <v>0.0927722089931362</v>
+        <v>0.0925220487147</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49456,19 +49456,19 @@
       </c>
       <c r="E223" s="22" t="n">
         <f aca="false">E219/E207</f>
-        <v>0.0788309809673693</v>
+        <v>0.0788593472919548</v>
       </c>
       <c r="F223" s="22" t="n">
         <f aca="false">F219/F207</f>
-        <v>0.0787673147540972</v>
+        <v>0.0788021824381109</v>
       </c>
       <c r="G223" s="22" t="n">
         <f aca="false">G219/G207</f>
-        <v>0.07874314023917</v>
+        <v>0.0787792002935899</v>
       </c>
       <c r="H223" s="29" t="n">
         <f aca="false">$G223+(fade_mA-$G223)*1/2</f>
-        <v>0.0787423262755345</v>
+        <v>0.0787603563027444</v>
       </c>
       <c r="I223" s="29" t="n">
         <f aca="false">$G223+(fade_mA-$G223)*2/2</f>
@@ -49488,15 +49488,15 @@
       </c>
       <c r="E224" s="33" t="n">
         <f aca="false">E200/(E193+E194)</f>
-        <v>10.8931999347519</v>
+        <v>10.7099463742892</v>
       </c>
       <c r="F224" s="33" t="n">
         <f aca="false">F200/(F193+F194)</f>
-        <v>11.2439200016107</v>
+        <v>11.0107983245925</v>
       </c>
       <c r="G224" s="33" t="n">
         <f aca="false">G200/(G193+G194)</f>
-        <v>10.7094429250466</v>
+        <v>10.4820606303431</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/dell/dist/20261025_戴爾模型_v0.1.xlsx
+++ b/dell/dist/20261025_戴爾模型_v0.1.xlsx
@@ -5218,26 +5218,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6451,26 +6451,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6631,26 +6631,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6752,26 +6752,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6873,26 +6873,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6994,26 +6994,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7115,26 +7115,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -33872,26 +33872,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/dell/dist/20261025_戴爾模型_v0.1.xlsx
+++ b/dell/dist/20261025_戴爾模型_v0.1.xlsx
@@ -17863,26 +17863,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">quanta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -18015,26 +18015,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">wistron/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">緯創模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">wistron/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">緯創個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -33948,26 +33948,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">quanta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">廣達模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">quanta/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">廣達個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -33986,26 +33986,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">wistron/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">緯創模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">wistron/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">緯創個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.2.xlsx</t>
     </r>
   </si>
   <si>
